--- a/artfynd/A 3648-2025 artfynd.xlsx
+++ b/artfynd/A 3648-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>122314189</v>
       </c>
       <c r="B3" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3648-2025 artfynd.xlsx
+++ b/artfynd/A 3648-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122314258</v>
+        <v>122314189</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>97151</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329317</v>
+        <v>329351</v>
       </c>
       <c r="R2" t="n">
-        <v>6426268</v>
+        <v>6426149</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,6 +781,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122314189</v>
+        <v>122314258</v>
       </c>
       <c r="B3" t="n">
-        <v>97139</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +812,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329351</v>
+        <v>329317</v>
       </c>
       <c r="R3" t="n">
-        <v>6426149</v>
+        <v>6426268</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +889,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +903,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3648-2025 artfynd.xlsx
+++ b/artfynd/A 3648-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122314189</v>
       </c>
       <c r="B2" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3648-2025 artfynd.xlsx
+++ b/artfynd/A 3648-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122314189</v>
+        <v>122314258</v>
       </c>
       <c r="B2" t="n">
-        <v>97156</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329351</v>
+        <v>329317</v>
       </c>
       <c r="R2" t="n">
-        <v>6426149</v>
+        <v>6426268</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +759,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +773,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122314258</v>
+        <v>122314189</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>97165</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,31 +803,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329317</v>
+        <v>329351</v>
       </c>
       <c r="R3" t="n">
-        <v>6426268</v>
+        <v>6426149</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,12 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,6 +892,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3648-2025 artfynd.xlsx
+++ b/artfynd/A 3648-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122314258</v>
+        <v>122314189</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>97178</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,26 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329317</v>
+        <v>329351</v>
       </c>
       <c r="R2" t="n">
-        <v>6426268</v>
+        <v>6426149</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,12 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,6 +781,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122314189</v>
+        <v>122314258</v>
       </c>
       <c r="B3" t="n">
-        <v>97165</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +812,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329351</v>
+        <v>329317</v>
       </c>
       <c r="R3" t="n">
-        <v>6426149</v>
+        <v>6426268</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +889,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +903,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3648-2025 artfynd.xlsx
+++ b/artfynd/A 3648-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122314189</v>
+        <v>122314258</v>
       </c>
       <c r="B2" t="n">
-        <v>97178</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329351</v>
+        <v>329317</v>
       </c>
       <c r="R2" t="n">
-        <v>6426149</v>
+        <v>6426268</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +778,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122314258</v>
+        <v>122314189</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>97191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,31 +808,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329317</v>
+        <v>329351</v>
       </c>
       <c r="R3" t="n">
-        <v>6426268</v>
+        <v>6426149</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,12 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,6 +902,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3648-2025 artfynd.xlsx
+++ b/artfynd/A 3648-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122314258</v>
+        <v>122314189</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>97191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329317</v>
+        <v>329351</v>
       </c>
       <c r="R2" t="n">
-        <v>6426268</v>
+        <v>6426149</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,6 +781,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122314189</v>
+        <v>122314258</v>
       </c>
       <c r="B3" t="n">
-        <v>97191</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +812,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329351</v>
+        <v>329317</v>
       </c>
       <c r="R3" t="n">
-        <v>6426149</v>
+        <v>6426268</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +889,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +903,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3648-2025 artfynd.xlsx
+++ b/artfynd/A 3648-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122314189</v>
+        <v>122314258</v>
       </c>
       <c r="B2" t="n">
-        <v>97191</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329351</v>
+        <v>329317</v>
       </c>
       <c r="R2" t="n">
-        <v>6426149</v>
+        <v>6426268</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår av födosök.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +778,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122314258</v>
+        <v>122314189</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>97194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,31 +808,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329317</v>
+        <v>329351</v>
       </c>
       <c r="R3" t="n">
-        <v>6426268</v>
+        <v>6426149</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,12 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår av födosök.</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,6 +902,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
